--- a/output/pdf_financials_xlsx/MERG.xlsx
+++ b/output/pdf_financials_xlsx/MERG.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-6.155105</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-6.155105</v>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-6.155105</v>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>37.715612</v>
+        <v>-37.715612</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>79.56701700000001</v>
+        <v>-79.56701700000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>83.6934</v>
+        <v>-83.6934</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>21.982518</v>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-6.155105</v>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-6.155105</v>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.026286</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.069445</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.364344</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.631562</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.720252</v>
       </c>
     </row>
     <row r="93">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-6.155105</v>
@@ -4058,7 +4058,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4464,7 +4468,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4675,7 +4683,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -5005,7 +5017,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>2.026286</v>
       </c>
@@ -8262,13 +8278,13 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>1.673868</v>
+        <v>-1.673868</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>6.155105</v>
+        <v>-6.155105</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -8651,10 +8667,10 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3.017249</v>
+        <v>-3.017249</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>4.774021</v>
+        <v>-4.774021</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MERG.xlsx
+++ b/output/pdf_financials_xlsx/MERG.xlsx
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.121246</v>
+        <v>3.018947</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.353702</v>
+        <v>5.357155</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.395913</v>
+        <v>1.673868</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.148552</v>
+        <v>6.191997</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.093027</v>
+        <v>2.166995</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.121246</v>
+        <v>-3.018947</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.353702</v>
+        <v>-5.357155</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.395913</v>
+        <v>-1.673868</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.148552</v>
+        <v>-6.191997</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.093027</v>
+        <v>-2.166995</v>
       </c>
     </row>
     <row r="12">
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.031874</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.040842</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.027218</v>
       </c>
     </row>
     <row r="13">
@@ -1025,13 +1025,13 @@
         <v>-4.774021</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.673868</v>
+        <v>-1.641994</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.155105</v>
+        <v>-6.114263</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.104348</v>
+        <v>-2.07713</v>
       </c>
     </row>
     <row r="28">
@@ -1069,13 +1069,13 @@
         <v>-4.774021</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.673868</v>
+        <v>-1.641994</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.155105</v>
+        <v>-6.114263</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.104348</v>
+        <v>-2.07713</v>
       </c>
     </row>
     <row r="30">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.014348</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.777482</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.735369</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.296913</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>9.660622999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.014348</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.777482</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.735369</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.296913</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>9.660622999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">

--- a/output/pdf_financials_xlsx/MERG.xlsx
+++ b/output/pdf_financials_xlsx/MERG.xlsx
@@ -2892,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.090351</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.462364</v>
       </c>
     </row>
     <row r="111">
@@ -3483,7 +3483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5769,7 +5769,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -8683,6 +8687,600 @@
         </is>
       </c>
       <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenses 6 $</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" s="5" t="n">
+        <v>0.681327</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Listing expenses 5</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>0.977521</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Investor relations 11</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>0.217132</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Management and consulting fees 11</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0.121246</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Audit, accounting and legal</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>0.103608</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Share-based compensation 10</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>0.910726</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Office expenses 11</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.007387</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES $</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>3.018947</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>(Loss) from operations for the period</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>-3.018947</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Flow-through share premium liability recovery</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>0.001698</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>NET (LOSS) FOR THE PERIOD $</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-3.017249</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>36.263482</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>(Loss) per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>-</t>
         </is>
